--- a/光伏配储项目/电价数据/2026/育新站.xlsx
+++ b/光伏配储项目/电价数据/2026/育新站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.75574</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5919500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.10025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42496</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44741</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50202</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12574</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13831</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14394</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07787999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11721</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20087</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05157</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.84964</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.33399</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2199</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23002</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21922</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.7518899999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44218</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15188</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6341599999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.72609</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.9716699999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73105</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.6799</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.32399</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9318200000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.66075</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.50821</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.74107</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.90003</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.14336</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.1995</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.65192</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.25879</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8697999999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79634</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75693</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5179600000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42529</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70809</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76571</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8701599999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5142899999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50227</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50252</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48479</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46694</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8667999999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7103400000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.80564</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43582</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.78062</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99497</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52596</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89581</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85096</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72729</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.40731</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08879</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03403</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47289</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5469700000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.50002</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9055700000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6251100000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.89176</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.15405</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.42315</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18112</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.03592</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.46935</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.3715</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.52691</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.30598</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.35647</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.91279</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.2489</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9014500000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.30993</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.3502</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.24116</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.0366</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78873</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80857</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50746</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48638</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47182</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.45197</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.57145</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.77536</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.7235900000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6563600000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24233</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5589700000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5017200000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8264400000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5967100000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72776</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81575</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.53128</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.53962</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8012100000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.12617</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.67735</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6014299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.7192200000000001</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51598</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50554</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5704600000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5960800000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5448500000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5648500000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26419</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61609</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.20223</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50575</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56572</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8660399999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.89935</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.42028</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.69782</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.72792</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.59411</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7854</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.82711</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5627000000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.13796</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.79991</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61752</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34194</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4931</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.49363</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.64723</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.54452</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.71823</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.9496100000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.66561</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.7288</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.09557</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.57641</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.21338</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.05396</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.96493</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.7603</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.18459</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.79239</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60301</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.73988</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.74863</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.67098</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.16254</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.15661</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42668</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52052</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8893</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.77651</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.17315</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.83109</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50036</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.68708</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.64662</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.5690499999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.48336</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.48612</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31749</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.6577999999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.74997</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20326</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22509</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15751</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40926</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18954</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.50903</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05559</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22456</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21326</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06392</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.11135</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.0716</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48479</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34359</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.58309</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21805</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20957</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07386</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07044</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33112</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31252</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78522</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88119</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.41274</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.85891</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.55675</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58357</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70594</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8762300000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46632</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81252</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5657000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85266</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.62361</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.62991</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5930299999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.32824</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34689</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9134800000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19765</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25355</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5295299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8647100000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44331</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13727</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68548</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77573</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6371599999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48927</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46025</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48601</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5226799999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15558</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.008869999999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5408099999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43107</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78259</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43226</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43498</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3064</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.23928</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23745</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27293</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22972</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.42861</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.42657</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33378</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48855</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.9963099999999999</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.68249</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25298</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.46345</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.46462</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.48742</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.6825800000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.76107</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7115900000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.87418</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6436799999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.90479</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.0648</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.62025</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34807</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47122</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.82578</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.95031</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9424400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.43541</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.8712000000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.50973</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.1919</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.95312</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.93743</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.16125</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.90855</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.35129</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.22033</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.86048</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.37517</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.55822</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6017100000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.31748</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29732</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.4516</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.71289</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.5726</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.45911</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.58902</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.26429</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.52993</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.87954</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.68448</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.6660700000000001</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.17319</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.64058</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.72911</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.65716</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.65158</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.15898</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.77795</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.43945</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7575499999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.73949</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.01447</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.6869700000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.6494500000000001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6043500000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.51497</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50295</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.92167</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30869</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.63802</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.9473200000000001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.7517999999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.04228</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.2999</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.97403</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49044</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.75364</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.74736</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34265</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.6858099999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.17412</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.51654</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41108</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.47222</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.46981</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.57553</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65028</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.5845399999999999</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.57343</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.8129299999999999</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.6624500000000001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33342</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.16888</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.73146</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.74513</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.58447</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.81576</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.60598</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.6446499999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51297</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.76627</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.6693300000000001</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.09816</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.6328400000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.6103099999999999</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.82308</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.6395700000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.81245</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.14491</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.14268</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.17415</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.94125</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8991</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.21668</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.7886299999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.02892</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.7983</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.59108</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.75224</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.78591</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.6971900000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.19351</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.12389</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6788200000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34963</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45216</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5235700000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47132</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.61095</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45597</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41827</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57172</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.12977</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.8238799999999999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.17701</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.21363</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.53833</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.29324</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.6466499999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.64871</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.6715099999999999</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.00022</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.76879</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.56235</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.5937100000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.58482</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.6642100000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.9132400000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.92371</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.25589</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.63766</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.6425299999999999</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.6313500000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.62814</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.12141</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46809</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61422</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7190299999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8068099999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57838</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70252</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.8532000000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.95826</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.72246</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76459</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6173099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6655800000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.03043</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.7328600000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43451</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45854</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.64338</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.60968</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.63107</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.62013</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.9013</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.6320800000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.7091900000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.6686799999999999</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.71924</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.64976</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15874</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22136</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.64024</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32878</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.10911</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.9095700000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.27248</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.25266</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25174</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18446</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24724</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09345000000000001</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25802</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03345</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19768</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.50652</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.49727</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3212</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.73907</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26643</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24532</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.23375</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.23681</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.23553</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.22997</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.23393</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23369</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16023</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26605</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02922</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03838</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01914</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20121</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26456</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23793</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32897</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7211799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.61953</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41829</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25598</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.4357200000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.65399</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.82085</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8755700000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.84917</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12357</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26621</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25765</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00588</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06386</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47102</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.48889</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79159</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.75237</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77511</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34024</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9963099999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7576900000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83612</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.78187</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83968</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83788</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8421900000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9394199999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.74091</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.7778200000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74421</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36199</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6018300000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.63182</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.56408</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49286</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45694</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47112</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27393</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44705</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.27597</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46386</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.73109</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6030399999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42353</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33647</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5457799999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7574299999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.53183</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56213</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.48657</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.49083</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.47046</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.46305</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.14268</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.6744199999999999</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.09067</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.93447</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.28727</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8207000000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.12373</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7211799999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5661799999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45346</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.68553</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.82826</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.98272</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.44846</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.10576</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.61975</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.42834</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.66077</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51381</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.88317</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7053400000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.75275</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.21488</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62646</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.35971</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.01063</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.2303</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.12289</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.04583</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.79883</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.7441</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.72358</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43612</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35572</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.22311</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.64775</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.13341</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.56399</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.94663</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.15082</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.59978</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.65857</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.23982</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.56825</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.53776</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.30209</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6580199999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.1457</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.74207</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5640700000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.13385</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.3428</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.14751</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.58466</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.46207</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.47116</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.11661</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.95686</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.63051</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.23946</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.55111</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.64834</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.64745</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.67515</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.11851</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46386</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.7079299999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.71865</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.65642</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.6957899999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.6596900000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.03735</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.52197</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36224</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.22489</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.9292899999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.73793</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.72049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.06019</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.29963</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.95387</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08645</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.01533</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.74998</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.7097899999999999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.48276</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.47875</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.43481</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6942999999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14511</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.5886399999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.9596399999999999</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.43491</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.63748</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58957</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.59958</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.5800700000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.56124</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.71024</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.60462</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.6031299999999999</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.71253</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.61815</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.62975</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.62534</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.7098099999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.7248300000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.26212</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.97989</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.79772</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.59383</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.71392</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.9549099999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38366</v>
       </c>
     </row>
   </sheetData>
